--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D819826-0E41-444E-85CC-5113AD7B4B57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7CE58D-EFCE-4C47-AC59-CD90A508527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="GRA-carbontax" sheetId="8" r:id="rId3"/>
     <sheet name="GRA-fueltax" sheetId="9" r:id="rId4"/>
     <sheet name="GRA-evsubsidy" sheetId="10" r:id="rId5"/>
-    <sheet name="GRA-vehbatsubsidy" sheetId="18" r:id="rId6"/>
+    <sheet name="GRA-batconsubsidy" sheetId="18" r:id="rId6"/>
     <sheet name="GRA-elecgensubsidy" sheetId="11" r:id="rId7"/>
     <sheet name="GRA-eleccapconstsubsidy" sheetId="12" r:id="rId8"/>
     <sheet name="GRA-distsolarsubsidy" sheetId="13" r:id="rId9"/>
@@ -407,9 +407,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -447,7 +447,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -553,7 +553,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -695,7 +695,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -712,17 +712,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="80.85546875" customWidth="1"/>
+    <col min="2" max="2" width="80.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -730,72 +730,72 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -803,7 +803,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>2</v>
       </c>
@@ -811,7 +811,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -819,7 +819,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>4</v>
       </c>
@@ -827,7 +827,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>5</v>
       </c>
@@ -835,114 +835,114 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B41" s="13"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>63</v>
       </c>
@@ -959,12 +959,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -972,7 +972,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -989,7 +989,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -997,7 +997,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1005,7 +1005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1024,12 +1024,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1037,7 +1037,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1089,12 +1089,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1154,12 +1154,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1167,7 +1167,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1176,7 +1176,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1184,7 +1184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1219,33 +1219,33 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1255,7 +1255,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>46</v>
       </c>
@@ -1275,7 +1275,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1315,7 +1315,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1335,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1355,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1395,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>34</v>
       </c>
@@ -1455,7 +1455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="12" t="s">
         <v>52</v>
       </c>
@@ -1465,12 +1465,12 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>46</v>
       </c>
@@ -1490,7 +1490,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1540,7 +1540,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1565,7 +1565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1590,7 +1590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1615,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1640,7 +1640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>42</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>34</v>
       </c>
@@ -1728,12 +1728,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1750,7 +1750,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1766,7 +1766,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1774,7 +1774,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1793,12 +1793,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1823,7 +1823,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1858,12 +1858,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1896,7 +1896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1923,12 +1923,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1936,7 +1936,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1945,7 +1945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1961,7 +1961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1969,7 +1969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -1988,12 +1988,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2001,7 +2001,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2010,7 +2010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2018,7 +2018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2026,7 +2026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2053,12 +2053,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2066,7 +2066,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2075,7 +2075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2083,7 +2083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>
@@ -2118,12 +2118,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="34.85546875" customWidth="1"/>
+    <col min="1" max="1" width="34.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2140,7 +2140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2156,7 +2156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>64</v>
       </c>

--- a/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
+++ b/InputData/ctrl-settings/GRA/Government Revenue Accounting.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ctrl-settings\GRA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7CE58D-EFCE-4C47-AC59-CD90A508527F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2B31A74-FEF5-46AA-8455-B6AF2D8FAC31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="698" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -47,26 +47,8 @@
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>tc={4F81BCB5-E56D-426A-91DB-BCF0877CB817}</author>
-  </authors>
-  <commentList>
-    <comment ref="C15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    It is recommended to leave this cell set to zero and to set a non-zero value in at least one other cell in this row.</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="63">
   <si>
     <t>GRA Government Revenue Accounting</t>
   </si>
@@ -249,15 +231,6 @@
   </si>
   <si>
     <t>lever.</t>
-  </si>
-  <si>
-    <t>It is recommended that you avoid using the "deficit spending" mechanism to handle "national debt</t>
-  </si>
-  <si>
-    <t>interest" to avoid creating a feedback loop where deficit spending increases debt, which increases</t>
-  </si>
-  <si>
-    <t>interest, which further increases debt, etc.</t>
   </si>
   <si>
     <t>Corporate Taxes</t>
@@ -311,7 +284,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -339,12 +312,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -381,7 +348,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -401,9 +368,7 @@
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <person displayName="Jeffrey Rissman" id="{B752AA03-E7FD-47E9-A7F9-587DA10781FB}" userId="S::jeff@energyinnovation.onmicrosoft.com::f3f117cb-d7f5-455c-900f-329d977050a0" providerId="AD"/>
-</personList>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -701,28 +666,20 @@
 </a:theme>
 </file>
 
-<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
-<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="C15" dT="2020-08-18T18:45:50.17" personId="{B752AA03-E7FD-47E9-A7F9-587DA10781FB}" id="{4F81BCB5-E56D-426A-91DB-BCF0877CB817}">
-    <text>It is recommended to leave this cell set to zero and to set a non-zero value in at least one other cell in this row.</text>
-  </threadedComment>
-</ThreadedComments>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B50"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B46"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="80.81640625" customWidth="1"/>
+    <col min="2" max="2" width="80.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -730,72 +687,72 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>1</v>
       </c>
@@ -803,7 +760,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>2</v>
       </c>
@@ -811,7 +768,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>3</v>
       </c>
@@ -819,7 +776,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>4</v>
       </c>
@@ -827,7 +784,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>5</v>
       </c>
@@ -835,116 +792,101 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>33</v>
       </c>
       <c r="B26" s="5"/>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="12" t="s">
         <v>55</v>
       </c>
       <c r="B41" s="13"/>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>60</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -959,12 +901,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -972,7 +914,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -981,7 +923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -989,7 +931,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -997,7 +939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1005,9 +947,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1024,12 +966,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1037,7 +979,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1046,7 +988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1054,7 +996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1062,7 +1004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1070,9 +1012,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1089,12 +1031,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1102,32 +1044,32 @@
         <v>42</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2">
         <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B15:F15)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
       <c r="B3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1135,9 +1077,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1154,12 +1096,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1167,16 +1109,16 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
       <c r="B2">
         <f t="array" ref="B2:B6">TRANSPOSE('Set Values Here'!B16:F16)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1184,15 +1126,15 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
       <c r="B4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1200,9 +1142,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1214,38 +1156,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="6" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>51</v>
       </c>
@@ -1255,7 +1197,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>46</v>
       </c>
@@ -1272,10 +1214,10 @@
         <v>50</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>35</v>
       </c>
@@ -1295,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1312,10 +1254,10 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>37</v>
       </c>
@@ -1335,7 +1277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>38</v>
       </c>
@@ -1355,7 +1297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>39</v>
       </c>
@@ -1375,7 +1317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1395,7 +1337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1415,18 +1357,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
       <c r="B15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C15" s="14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D15">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1435,18 +1377,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>34</v>
       </c>
       <c r="B16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C16">
         <v>5</v>
       </c>
       <c r="D16">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1455,7 +1397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
         <v>52</v>
       </c>
@@ -1465,12 +1407,12 @@
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="29" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>46</v>
       </c>
@@ -1487,10 +1429,10 @@
         <v>50</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>35</v>
       </c>
@@ -1515,7 +1457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -1525,7 +1467,7 @@
       </c>
       <c r="C23" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="D23" s="10">
         <f t="shared" si="1"/>
@@ -1537,10 +1479,10 @@
       </c>
       <c r="F23" s="10">
         <f t="shared" si="1"/>
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1565,7 +1507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>38</v>
       </c>
@@ -1590,7 +1532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>39</v>
       </c>
@@ -1615,7 +1557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>40</v>
       </c>
@@ -1640,7 +1582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>41</v>
       </c>
@@ -1665,21 +1607,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>42</v>
       </c>
       <c r="B29" s="10">
         <f t="shared" ref="B29:F29" si="7">IFERROR(B15/SUM($B15:$F15),1/COUNT($B15:$F15))</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="C29" s="10">
         <f t="shared" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D29" s="10">
         <f t="shared" si="7"/>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E29" s="10">
         <f t="shared" si="7"/>
@@ -1690,21 +1632,21 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="10">
         <f t="shared" ref="B30:F30" si="8">IFERROR(B16/SUM($B16:$F16),1/COUNT($B16:$F16))</f>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="C30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>1</v>
       </c>
       <c r="D30" s="10">
         <f t="shared" si="8"/>
-        <v>0.33333333333333331</v>
+        <v>0</v>
       </c>
       <c r="E30" s="10">
         <f t="shared" si="8"/>
@@ -1718,7 +1660,6 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -1728,12 +1669,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1741,7 +1682,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1750,7 +1691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1758,7 +1699,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1766,7 +1707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1774,9 +1715,9 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1793,12 +1734,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1806,7 +1747,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1815,7 +1756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1823,7 +1764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1831,7 +1772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1839,12 +1780,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1858,12 +1799,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1871,7 +1812,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1880,7 +1821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1888,7 +1829,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1896,7 +1837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1904,9 +1845,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1923,12 +1864,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -1936,7 +1877,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -1945,7 +1886,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -1953,7 +1894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1961,7 +1902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -1969,9 +1910,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1988,12 +1929,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2001,7 +1942,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2010,7 +1951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2018,7 +1959,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2026,7 +1967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2034,9 +1975,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2053,12 +1994,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2066,7 +2007,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2075,7 +2016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2083,7 +2024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2091,7 +2032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2099,9 +2040,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -2118,12 +2059,12 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>23</v>
       </c>
@@ -2131,7 +2072,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>47</v>
       </c>
@@ -2140,7 +2081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>48</v>
       </c>
@@ -2148,7 +2089,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -2156,7 +2097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>50</v>
       </c>
@@ -2164,9 +2105,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6">
         <v>0</v>
